--- a/25-신분당-강남구-보고서.xlsx
+++ b/25-신분당-강남구-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:T21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,13 +485,13 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="str">
         <v>강남대로</v>
       </c>
       <c r="C5" t="str">
-        <v>25-강남구-1</v>
+        <v>25-강남구-2</v>
       </c>
       <c r="D5" t="str">
         <v>양호</v>
@@ -533,27 +533,27 @@
         <v/>
       </c>
       <c r="Q5" t="str">
-        <v>역삼동 858</v>
+        <v>역삼동 826</v>
       </c>
       <c r="R5" t="str">
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>강남역 교차로 도로</v>
+        <v>올리브영 강남중앙점 도로</v>
       </c>
       <c r="T5" t="str">
         <v/>
       </c>
     </row>
-    <row r="6">
+    <row r="6" xml:space="preserve">
       <c r="A6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="str">
         <v>강남대로</v>
       </c>
       <c r="C6" t="str">
-        <v>25-강남구-2</v>
+        <v>25-강남구-3</v>
       </c>
       <c r="D6" t="str">
         <v>양호</v>
@@ -595,97 +595,97 @@
         <v/>
       </c>
       <c r="Q6" t="str">
-        <v>역삼동 826</v>
+        <v>역삼동 831</v>
       </c>
       <c r="R6" t="str">
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>올리브영 강남중앙점 도로</v>
-      </c>
-      <c r="T6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="B7" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C7" t="str">
-        <v>25-강남구-3</v>
-      </c>
-      <c r="D7" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E7" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F7" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G7" t="str">
-        <v>13.5</v>
-      </c>
-      <c r="H7" t="str">
-        <v>-</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>4</v>
-      </c>
-      <c r="O7" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P7" t="str">
-        <v/>
-      </c>
-      <c r="Q7" t="str">
-        <v>역삼동 831</v>
-      </c>
-      <c r="R7" t="str">
-        <v/>
-      </c>
-      <c r="S7" t="str">
         <v>혜천빌딩 앞 도로</v>
       </c>
-      <c r="T7" t="str" xml:space="preserve">
+      <c r="T6" t="str" xml:space="preserve">
         <v xml:space="preserve">22년 발생 첫조사_x000d_
 '23년 아스콘 보수(패칭)_x000d_
 '25년 아스콘 재보수(패칭)</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C7" t="str">
+        <v>25-강남구-4</v>
+      </c>
+      <c r="D7" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E7" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F7" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G7" t="str">
+        <v>13.5</v>
+      </c>
+      <c r="H7" t="str">
+        <v>-</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>4</v>
+      </c>
+      <c r="O7" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v>강남대로 350</v>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
+        <v>스케일타워 앞 도로</v>
+      </c>
+      <c r="T7" t="str">
+        <v/>
+      </c>
+    </row>
     <row r="8">
       <c r="A8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" t="str">
         <v>강남대로</v>
       </c>
       <c r="C8" t="str">
-        <v>25-강남구-4</v>
+        <v>25-강남구-5</v>
       </c>
       <c r="D8" t="str">
         <v>양호</v>
       </c>
       <c r="E8" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F8" t="str">
         <v>양호</v>
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -712,7 +712,7 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O8" t="str">
         <v>일반</v>
@@ -721,13 +721,13 @@
         <v/>
       </c>
       <c r="Q8" t="str">
-        <v>강남대로 350</v>
+        <v>역삼동 831-18</v>
       </c>
       <c r="R8" t="str">
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>스케일타워 앞 도로</v>
+        <v>역삼빌딩 앞 도로</v>
       </c>
       <c r="T8" t="str">
         <v/>
@@ -735,19 +735,19 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="str">
         <v>강남대로</v>
       </c>
       <c r="C9" t="str">
-        <v>25-강남구-5</v>
+        <v>25-강남구-6</v>
       </c>
       <c r="D9" t="str">
         <v>양호</v>
       </c>
       <c r="E9" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F9" t="str">
         <v>양호</v>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -774,7 +774,7 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O9" t="str">
         <v>일반</v>
@@ -783,13 +783,13 @@
         <v/>
       </c>
       <c r="Q9" t="str">
-        <v>역삼동 831-18</v>
+        <v>역삼동 832</v>
       </c>
       <c r="R9" t="str">
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>역삼빌딩 앞 도로</v>
+        <v>우성아파트 앞 사거리 도로</v>
       </c>
       <c r="T9" t="str">
         <v/>
@@ -797,13 +797,13 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" t="str">
         <v>강남대로</v>
       </c>
       <c r="C10" t="str">
-        <v>25-강남구-6</v>
+        <v>25-강남구-7</v>
       </c>
       <c r="D10" t="str">
         <v>양호</v>
@@ -845,13 +845,13 @@
         <v/>
       </c>
       <c r="Q10" t="str">
-        <v>역삼동 832</v>
+        <v>역삼동 832-2</v>
       </c>
       <c r="R10" t="str">
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>우성아파트 앞 사거리 도로</v>
+        <v>역삼동832-2 알 도로</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -859,13 +859,13 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" t="str">
         <v>강남대로</v>
       </c>
       <c r="C11" t="str">
-        <v>25-강남구-7</v>
+        <v>25-강남구-8</v>
       </c>
       <c r="D11" t="str">
         <v>양호</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="Q11" t="str">
-        <v>역삼동 832-2</v>
+        <v>역삼동 837</v>
       </c>
       <c r="R11" t="str">
         <v/>
       </c>
       <c r="S11" t="str">
-        <v>역삼동832-2 알 도로</v>
+        <v>라온약국 앞 도로</v>
       </c>
       <c r="T11" t="str">
         <v/>
@@ -921,13 +921,13 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" t="str">
         <v>강남대로</v>
       </c>
       <c r="C12" t="str">
-        <v>25-강남구-8</v>
+        <v>25-강남구-9</v>
       </c>
       <c r="D12" t="str">
         <v>양호</v>
@@ -966,16 +966,16 @@
         <v>일반</v>
       </c>
       <c r="P12" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q12" t="str">
-        <v>역삼동 837</v>
+        <v>역삼동 837-11</v>
       </c>
       <c r="R12" t="str">
         <v/>
       </c>
       <c r="S12" t="str">
-        <v>라온약국 앞 도로</v>
+        <v>유니온센터 주차장 입구 앞 도로</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -983,13 +983,13 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" t="str">
         <v>강남대로</v>
       </c>
       <c r="C13" t="str">
-        <v>25-강남구-9</v>
+        <v>25-강남구-10</v>
       </c>
       <c r="D13" t="str">
         <v>양호</v>
@@ -1028,16 +1028,16 @@
         <v>일반</v>
       </c>
       <c r="P13" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q13" t="str">
-        <v>역삼동 837-11</v>
+        <v>역삼동 837-36</v>
       </c>
       <c r="R13" t="str">
         <v/>
       </c>
       <c r="S13" t="str">
-        <v>유니온센터 주차장 입구 앞 도로</v>
+        <v>우리은행 앞 도로</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -1045,13 +1045,13 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" t="str">
         <v>강남대로</v>
       </c>
       <c r="C14" t="str">
-        <v>25-강남구-10</v>
+        <v>25-강남구-11</v>
       </c>
       <c r="D14" t="str">
         <v>양호</v>
@@ -1093,13 +1093,13 @@
         <v/>
       </c>
       <c r="Q14" t="str">
-        <v>역삼동 837-36</v>
+        <v>역삼동 838</v>
       </c>
       <c r="R14" t="str">
         <v/>
       </c>
       <c r="S14" t="str">
-        <v>우리은행 앞 도로</v>
+        <v>뱅뱅사거리 도로</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -1107,13 +1107,13 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" t="str">
         <v>강남대로</v>
       </c>
       <c r="C15" t="str">
-        <v>25-강남구-11</v>
+        <v>25-강남구-12</v>
       </c>
       <c r="D15" t="str">
         <v>양호</v>
@@ -1155,13 +1155,13 @@
         <v/>
       </c>
       <c r="Q15" t="str">
-        <v>뱅뱅사거리</v>
+        <v>도곡동 946</v>
       </c>
       <c r="R15" t="str">
         <v/>
       </c>
       <c r="S15" t="str">
-        <v>뱅뱅사거리 도로</v>
+        <v>부영빌딩 앞 도로</v>
       </c>
       <c r="T15" t="str">
         <v/>
@@ -1169,13 +1169,13 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" t="str">
         <v>강남대로</v>
       </c>
       <c r="C16" t="str">
-        <v>25-강남구-12</v>
+        <v>25-강남구-13</v>
       </c>
       <c r="D16" t="str">
         <v>양호</v>
@@ -1217,13 +1217,13 @@
         <v/>
       </c>
       <c r="Q16" t="str">
-        <v>도곡동 946</v>
+        <v>도곡동 949</v>
       </c>
       <c r="R16" t="str">
         <v/>
       </c>
       <c r="S16" t="str">
-        <v>부영빌딩 앞 도로</v>
+        <v>메디움강남 요양병원 앞 도로</v>
       </c>
       <c r="T16" t="str">
         <v/>
@@ -1231,19 +1231,19 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" t="str">
         <v>강남대로</v>
       </c>
       <c r="C17" t="str">
-        <v>25-강남구-13</v>
+        <v>25-강남구-14</v>
       </c>
       <c r="D17" t="str">
         <v>양호</v>
       </c>
       <c r="E17" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F17" t="str">
         <v>양호</v>
@@ -1258,7 +1258,7 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O17" t="str">
         <v>일반</v>
@@ -1279,13 +1279,13 @@
         <v/>
       </c>
       <c r="Q17" t="str">
-        <v>도곡동 949</v>
+        <v>도곡동 949-3</v>
       </c>
       <c r="R17" t="str">
         <v/>
       </c>
       <c r="S17" t="str">
-        <v>메디움강남 요양병원 앞 도로</v>
+        <v>캠코양재타워 주차장 앞 도로</v>
       </c>
       <c r="T17" t="str">
         <v/>
@@ -1293,19 +1293,19 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" t="str">
         <v>강남대로</v>
       </c>
       <c r="C18" t="str">
-        <v>25-강남구-14</v>
+        <v>25-강남구-15</v>
       </c>
       <c r="D18" t="str">
         <v>양호</v>
       </c>
       <c r="E18" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F18" t="str">
         <v>양호</v>
@@ -1320,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="N18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O18" t="str">
         <v>일반</v>
@@ -1347,7 +1347,7 @@
         <v/>
       </c>
       <c r="S18" t="str">
-        <v>캠코양재타워 주차장 앞 도로</v>
+        <v>한국자산관리공사 앞 도로</v>
       </c>
       <c r="T18" t="str">
         <v/>
@@ -1355,13 +1355,13 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19" t="str">
         <v>강남대로</v>
       </c>
       <c r="C19" t="str">
-        <v>25-강남구-15</v>
+        <v>25-강남구-16</v>
       </c>
       <c r="D19" t="str">
         <v>양호</v>
@@ -1403,13 +1403,13 @@
         <v/>
       </c>
       <c r="Q19" t="str">
-        <v>도곡동 949-3</v>
+        <v>도곡동 952-6</v>
       </c>
       <c r="R19" t="str">
         <v/>
       </c>
       <c r="S19" t="str">
-        <v>한국자산관리공사 앞 도로</v>
+        <v>도루코본사 앞 도로</v>
       </c>
       <c r="T19" t="str">
         <v/>
@@ -1417,13 +1417,13 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20" t="str">
         <v>강남대로</v>
       </c>
       <c r="C20" t="str">
-        <v>25-강남구-16</v>
+        <v>25-강남구-17</v>
       </c>
       <c r="D20" t="str">
         <v>양호</v>
@@ -1465,13 +1465,13 @@
         <v/>
       </c>
       <c r="Q20" t="str">
-        <v>도곡동 952-6</v>
+        <v>도곡동 953</v>
       </c>
       <c r="R20" t="str">
         <v/>
       </c>
       <c r="S20" t="str">
-        <v>도루코본사 앞 도로</v>
+        <v>강남 현안과의원 앞 도로</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -1479,13 +1479,13 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B21" t="str">
         <v>강남대로</v>
       </c>
       <c r="C21" t="str">
-        <v>25-강남구-17</v>
+        <v>25-강남구-18</v>
       </c>
       <c r="D21" t="str">
         <v>양호</v>
@@ -1527,83 +1527,21 @@
         <v/>
       </c>
       <c r="Q21" t="str">
-        <v>도곡동 953</v>
+        <v>도곡동 958-34</v>
       </c>
       <c r="R21" t="str">
         <v/>
       </c>
       <c r="S21" t="str">
-        <v>강남 현안과의원 앞 도로</v>
+        <v>양재역 #3번 출구 앞 도로</v>
       </c>
       <c r="T21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>18</v>
-      </c>
-      <c r="B22" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C22" t="str">
-        <v>25-강남구-18</v>
-      </c>
-      <c r="D22" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E22" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F22" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G22" t="str">
-        <v>13.5</v>
-      </c>
-      <c r="H22" t="str">
-        <v>-</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>3</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>1</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>4</v>
-      </c>
-      <c r="O22" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P22" t="str">
-        <v/>
-      </c>
-      <c r="Q22" t="str">
-        <v>도곡동 958-34</v>
-      </c>
-      <c r="R22" t="str">
-        <v/>
-      </c>
-      <c r="S22" t="str">
-        <v>양재역 #3번 출구 앞 도로</v>
-      </c>
-      <c r="T22" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T21"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-신분당-강남구-보고서.xlsx
+++ b/25-신분당-강남구-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T38"/>
+  <dimension ref="A1:T37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,13 +485,13 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="str">
         <v>강남대로</v>
       </c>
       <c r="C5" t="str">
-        <v>25-강남구-1</v>
+        <v>25-강남구-2</v>
       </c>
       <c r="D5" t="str">
         <v>양호</v>
@@ -533,27 +533,27 @@
         <v/>
       </c>
       <c r="Q5" t="str">
-        <v>역삼동 858</v>
+        <v>역삼동 826</v>
       </c>
       <c r="R5" t="str">
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>강남역 교차로 도로</v>
+        <v>올리브영 강남중앙점 도로</v>
       </c>
       <c r="T5" t="str">
         <v/>
       </c>
     </row>
-    <row r="6">
+    <row r="6" xml:space="preserve">
       <c r="A6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="str">
         <v>강남대로</v>
       </c>
       <c r="C6" t="str">
-        <v>25-강남구-2</v>
+        <v>25-강남구-3</v>
       </c>
       <c r="D6" t="str">
         <v>양호</v>
@@ -595,97 +595,97 @@
         <v/>
       </c>
       <c r="Q6" t="str">
-        <v>역삼동 826</v>
+        <v>역삼동 831</v>
       </c>
       <c r="R6" t="str">
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>올리브영 강남중앙점 도로</v>
-      </c>
-      <c r="T6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="B7" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C7" t="str">
-        <v>25-강남구-3</v>
-      </c>
-      <c r="D7" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E7" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F7" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G7" t="str">
-        <v>13.5</v>
-      </c>
-      <c r="H7" t="str">
-        <v>-</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>4</v>
-      </c>
-      <c r="O7" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P7" t="str">
-        <v/>
-      </c>
-      <c r="Q7" t="str">
-        <v>역삼동 831</v>
-      </c>
-      <c r="R7" t="str">
-        <v/>
-      </c>
-      <c r="S7" t="str">
         <v>혜천빌딩 앞 도로</v>
       </c>
-      <c r="T7" t="str" xml:space="preserve">
+      <c r="T6" t="str" xml:space="preserve">
         <v xml:space="preserve">22년 발생 첫조사_x000d_
 '23년 아스콘 보수(패칭)_x000d_
 '25년 아스콘 재보수(패칭)</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C7" t="str">
+        <v>25-강남구-4</v>
+      </c>
+      <c r="D7" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E7" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F7" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G7" t="str">
+        <v>13.5</v>
+      </c>
+      <c r="H7" t="str">
+        <v>-</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>4</v>
+      </c>
+      <c r="O7" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v>강남대로 350</v>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
+        <v>스케일타워 앞 도로</v>
+      </c>
+      <c r="T7" t="str">
+        <v/>
+      </c>
+    </row>
     <row r="8">
       <c r="A8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" t="str">
         <v>강남대로</v>
       </c>
       <c r="C8" t="str">
-        <v>25-강남구-4</v>
+        <v>25-강남구-5</v>
       </c>
       <c r="D8" t="str">
         <v>양호</v>
       </c>
       <c r="E8" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F8" t="str">
         <v>양호</v>
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -712,7 +712,7 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O8" t="str">
         <v>일반</v>
@@ -721,13 +721,13 @@
         <v/>
       </c>
       <c r="Q8" t="str">
-        <v>강남대로 350</v>
+        <v>역삼동 831-18</v>
       </c>
       <c r="R8" t="str">
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>스케일타워 앞 도로</v>
+        <v>역삼빌딩 앞 도로</v>
       </c>
       <c r="T8" t="str">
         <v/>
@@ -735,19 +735,19 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="str">
         <v>강남대로</v>
       </c>
       <c r="C9" t="str">
-        <v>25-강남구-5</v>
+        <v>25-강남구-6</v>
       </c>
       <c r="D9" t="str">
         <v>양호</v>
       </c>
       <c r="E9" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F9" t="str">
         <v>양호</v>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -774,7 +774,7 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O9" t="str">
         <v>일반</v>
@@ -783,13 +783,13 @@
         <v/>
       </c>
       <c r="Q9" t="str">
-        <v>역삼동 831-18</v>
+        <v>역삼동 832</v>
       </c>
       <c r="R9" t="str">
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>역삼빌딩 앞 도로</v>
+        <v>우성아파트 앞 사거리 도로</v>
       </c>
       <c r="T9" t="str">
         <v/>
@@ -797,13 +797,13 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" t="str">
         <v>강남대로</v>
       </c>
       <c r="C10" t="str">
-        <v>25-강남구-6</v>
+        <v>25-강남구-7</v>
       </c>
       <c r="D10" t="str">
         <v>양호</v>
@@ -845,13 +845,13 @@
         <v/>
       </c>
       <c r="Q10" t="str">
-        <v>역삼동 832</v>
+        <v>역삼동 832-2</v>
       </c>
       <c r="R10" t="str">
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>우성아파트 앞 사거리 도로</v>
+        <v>역삼동832-2 알 도로</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -859,13 +859,13 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" t="str">
         <v>강남대로</v>
       </c>
       <c r="C11" t="str">
-        <v>25-강남구-7</v>
+        <v>25-강남구-8</v>
       </c>
       <c r="D11" t="str">
         <v>양호</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="Q11" t="str">
-        <v>역삼동 832-2</v>
+        <v>역삼동 837</v>
       </c>
       <c r="R11" t="str">
         <v/>
       </c>
       <c r="S11" t="str">
-        <v>역삼동832-2 알 도로</v>
+        <v>라온약국 앞 도로</v>
       </c>
       <c r="T11" t="str">
         <v/>
@@ -921,13 +921,13 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" t="str">
         <v>강남대로</v>
       </c>
       <c r="C12" t="str">
-        <v>25-강남구-8</v>
+        <v>25-강남구-9</v>
       </c>
       <c r="D12" t="str">
         <v>양호</v>
@@ -966,16 +966,16 @@
         <v>일반</v>
       </c>
       <c r="P12" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q12" t="str">
-        <v>역삼동 837</v>
+        <v>역삼동 837-11</v>
       </c>
       <c r="R12" t="str">
         <v/>
       </c>
       <c r="S12" t="str">
-        <v>라온약국 앞 도로</v>
+        <v>유니온센터 주차장 입구 앞 도로</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -983,13 +983,13 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" t="str">
         <v>강남대로</v>
       </c>
       <c r="C13" t="str">
-        <v>25-강남구-9</v>
+        <v>25-강남구-10</v>
       </c>
       <c r="D13" t="str">
         <v>양호</v>
@@ -1028,16 +1028,16 @@
         <v>일반</v>
       </c>
       <c r="P13" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q13" t="str">
-        <v>역삼동 837-11</v>
+        <v>역삼동 837-36</v>
       </c>
       <c r="R13" t="str">
         <v/>
       </c>
       <c r="S13" t="str">
-        <v>유니온센터 주차장 입구 앞 도로</v>
+        <v>우리은행 앞 도로</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -1045,13 +1045,13 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" t="str">
         <v>강남대로</v>
       </c>
       <c r="C14" t="str">
-        <v>25-강남구-10</v>
+        <v>25-강남구-11</v>
       </c>
       <c r="D14" t="str">
         <v>양호</v>
@@ -1093,13 +1093,13 @@
         <v/>
       </c>
       <c r="Q14" t="str">
-        <v>역삼동 837-36</v>
+        <v>역삼동 838</v>
       </c>
       <c r="R14" t="str">
         <v/>
       </c>
       <c r="S14" t="str">
-        <v>우리은행 앞 도로</v>
+        <v>뱅뱅사거리 도로</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -1107,13 +1107,13 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" t="str">
         <v>강남대로</v>
       </c>
       <c r="C15" t="str">
-        <v>25-강남구-11</v>
+        <v>25-강남구-12</v>
       </c>
       <c r="D15" t="str">
         <v>양호</v>
@@ -1155,13 +1155,13 @@
         <v/>
       </c>
       <c r="Q15" t="str">
-        <v>역삼동 838</v>
+        <v>도곡동 946</v>
       </c>
       <c r="R15" t="str">
         <v/>
       </c>
       <c r="S15" t="str">
-        <v>뱅뱅사거리 도로</v>
+        <v>부영빌딩 앞 도로</v>
       </c>
       <c r="T15" t="str">
         <v/>
@@ -1169,13 +1169,13 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" t="str">
         <v>강남대로</v>
       </c>
       <c r="C16" t="str">
-        <v>25-강남구-12</v>
+        <v>25-강남구-13</v>
       </c>
       <c r="D16" t="str">
         <v>양호</v>
@@ -1217,13 +1217,13 @@
         <v/>
       </c>
       <c r="Q16" t="str">
-        <v>도곡동 946</v>
+        <v>도곡동 949</v>
       </c>
       <c r="R16" t="str">
         <v/>
       </c>
       <c r="S16" t="str">
-        <v>부영빌딩 앞 도로</v>
+        <v>메디움강남 요양병원 앞 도로</v>
       </c>
       <c r="T16" t="str">
         <v/>
@@ -1231,19 +1231,19 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" t="str">
         <v>강남대로</v>
       </c>
       <c r="C17" t="str">
-        <v>25-강남구-13</v>
+        <v>25-강남구-14</v>
       </c>
       <c r="D17" t="str">
         <v>양호</v>
       </c>
       <c r="E17" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F17" t="str">
         <v>양호</v>
@@ -1258,7 +1258,7 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O17" t="str">
         <v>일반</v>
@@ -1279,13 +1279,13 @@
         <v/>
       </c>
       <c r="Q17" t="str">
-        <v>도곡동 949</v>
+        <v>도곡동 949-3</v>
       </c>
       <c r="R17" t="str">
         <v/>
       </c>
       <c r="S17" t="str">
-        <v>메디움강남 요양병원 앞 도로</v>
+        <v>캠코양재타워 주차장 앞 도로</v>
       </c>
       <c r="T17" t="str">
         <v/>
@@ -1293,19 +1293,19 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" t="str">
         <v>강남대로</v>
       </c>
       <c r="C18" t="str">
-        <v>25-강남구-14</v>
+        <v>25-강남구-15</v>
       </c>
       <c r="D18" t="str">
         <v>양호</v>
       </c>
       <c r="E18" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F18" t="str">
         <v>양호</v>
@@ -1320,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="N18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O18" t="str">
         <v>일반</v>
@@ -1347,7 +1347,7 @@
         <v/>
       </c>
       <c r="S18" t="str">
-        <v>캠코양재타워 주차장 앞 도로</v>
+        <v>한국자산관리공사 앞 도로</v>
       </c>
       <c r="T18" t="str">
         <v/>
@@ -1355,13 +1355,13 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19" t="str">
         <v>강남대로</v>
       </c>
       <c r="C19" t="str">
-        <v>25-강남구-15</v>
+        <v>25-강남구-16</v>
       </c>
       <c r="D19" t="str">
         <v>양호</v>
@@ -1403,13 +1403,13 @@
         <v/>
       </c>
       <c r="Q19" t="str">
-        <v>도곡동 949-3</v>
+        <v>도곡동 952-6</v>
       </c>
       <c r="R19" t="str">
         <v/>
       </c>
       <c r="S19" t="str">
-        <v>한국자산관리공사 앞 도로</v>
+        <v>도루코본사 앞 도로</v>
       </c>
       <c r="T19" t="str">
         <v/>
@@ -1417,13 +1417,13 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20" t="str">
         <v>강남대로</v>
       </c>
       <c r="C20" t="str">
-        <v>25-강남구-16</v>
+        <v>25-강남구-17</v>
       </c>
       <c r="D20" t="str">
         <v>양호</v>
@@ -1465,13 +1465,13 @@
         <v/>
       </c>
       <c r="Q20" t="str">
-        <v>도곡동 952-6</v>
+        <v>도곡동 953</v>
       </c>
       <c r="R20" t="str">
         <v/>
       </c>
       <c r="S20" t="str">
-        <v>도루코본사 앞 도로</v>
+        <v>강남 현안과의원 앞 도로</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -1479,13 +1479,13 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B21" t="str">
         <v>강남대로</v>
       </c>
       <c r="C21" t="str">
-        <v>25-강남구-17</v>
+        <v>25-강남구-18</v>
       </c>
       <c r="D21" t="str">
         <v>양호</v>
@@ -1527,27 +1527,27 @@
         <v/>
       </c>
       <c r="Q21" t="str">
-        <v>도곡동 953</v>
+        <v>도곡동 958-34</v>
       </c>
       <c r="R21" t="str">
         <v/>
       </c>
       <c r="S21" t="str">
-        <v>강남 현안과의원 앞 도로</v>
+        <v>양재역 #3번 출구 앞 도로</v>
       </c>
       <c r="T21" t="str">
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>18</v>
+      <c r="A22" t="str">
+        <v>26-01</v>
       </c>
       <c r="B22" t="str">
         <v>강남대로</v>
       </c>
       <c r="C22" t="str">
-        <v>25-강남구-18</v>
+        <v>26-강남구-01</v>
       </c>
       <c r="D22" t="str">
         <v>양호</v>
@@ -1559,43 +1559,43 @@
         <v>양호</v>
       </c>
       <c r="G22" t="str">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="H22" t="str">
         <v>-</v>
       </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>3</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>1</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
+      <c r="I22" t="str">
+        <v>0</v>
+      </c>
+      <c r="J22" t="str">
+        <v>3</v>
+      </c>
+      <c r="K22" t="str">
+        <v>0</v>
+      </c>
+      <c r="L22" t="str">
+        <v>1</v>
+      </c>
+      <c r="M22" t="str">
+        <v>0</v>
+      </c>
+      <c r="N22" t="str">
         <v>4</v>
       </c>
       <c r="O22" t="str">
         <v>일반</v>
       </c>
       <c r="P22" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="Q22" t="str">
-        <v>도곡동 958-34</v>
+        <v>역삼동825-13</v>
       </c>
       <c r="R22" t="str">
         <v/>
       </c>
       <c r="S22" t="str">
-        <v>양재역 #3번 출구 앞 도로</v>
+        <v>강남센터빌딩 KB은행 앞도로(강남대로388)</v>
       </c>
       <c r="T22" t="str">
         <v/>
@@ -1603,13 +1603,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>26-01</v>
+        <v>26-02</v>
       </c>
       <c r="B23" t="str">
         <v>강남대로</v>
       </c>
       <c r="C23" t="str">
-        <v>26-강남구-01</v>
+        <v>26-강남구-02</v>
       </c>
       <c r="D23" t="str">
         <v>양호</v>
@@ -1651,13 +1651,13 @@
         <v>-</v>
       </c>
       <c r="Q23" t="str">
-        <v>역삼동825-13</v>
+        <v>역삼동825-2</v>
       </c>
       <c r="R23" t="str">
         <v/>
       </c>
       <c r="S23" t="str">
-        <v>강남센터빌딩 KB은행 앞도로(강남대로388)</v>
+        <v>메리츠타워 앞도로(강남대로382)</v>
       </c>
       <c r="T23" t="str">
         <v/>
@@ -1665,13 +1665,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>26-02</v>
+        <v>26-03</v>
       </c>
       <c r="B24" t="str">
         <v>강남대로</v>
       </c>
       <c r="C24" t="str">
-        <v>26-강남구-02</v>
+        <v>26-강남구-03</v>
       </c>
       <c r="D24" t="str">
         <v>양호</v>
@@ -1713,13 +1713,13 @@
         <v>-</v>
       </c>
       <c r="Q24" t="str">
-        <v>역삼동825-2</v>
+        <v>역삼동826</v>
       </c>
       <c r="R24" t="str">
         <v/>
       </c>
       <c r="S24" t="str">
-        <v>메리츠타워 앞도로(강남대로382)</v>
+        <v>케이스퀘어강남2 앞 도로(강남대로374)</v>
       </c>
       <c r="T24" t="str">
         <v/>
@@ -1727,13 +1727,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>26-03</v>
+        <v>26-04</v>
       </c>
       <c r="B25" t="str">
         <v>강남대로</v>
       </c>
       <c r="C25" t="str">
-        <v>26-강남구-03</v>
+        <v>26-강남구-04</v>
       </c>
       <c r="D25" t="str">
         <v>양호</v>
@@ -1775,13 +1775,13 @@
         <v>-</v>
       </c>
       <c r="Q25" t="str">
-        <v>역삼동826</v>
+        <v>역삼동826-24</v>
       </c>
       <c r="R25" t="str">
         <v/>
       </c>
       <c r="S25" t="str">
-        <v>케이스퀘어강남2 앞 도로(강남대로374)</v>
+        <v>화이트타워 앞 도로(강남대로372)</v>
       </c>
       <c r="T25" t="str">
         <v/>
@@ -1789,13 +1789,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>26-04</v>
+        <v>26-05</v>
       </c>
       <c r="B26" t="str">
         <v>강남대로</v>
       </c>
       <c r="C26" t="str">
-        <v>26-강남구-04</v>
+        <v>26-강남구-05</v>
       </c>
       <c r="D26" t="str">
         <v>양호</v>
@@ -1837,13 +1837,13 @@
         <v>-</v>
       </c>
       <c r="Q26" t="str">
-        <v>역삼동826-24</v>
+        <v>역삼동826-21</v>
       </c>
       <c r="R26" t="str">
         <v/>
       </c>
       <c r="S26" t="str">
-        <v>화이트타워 앞 도로(강남대로372)</v>
+        <v>미왕빌딩 앞 도로(강남대로364)</v>
       </c>
       <c r="T26" t="str">
         <v/>
@@ -1851,13 +1851,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>26-05</v>
+        <v>26-06</v>
       </c>
       <c r="B27" t="str">
         <v>강남대로</v>
       </c>
       <c r="C27" t="str">
-        <v>26-강남구-05</v>
+        <v>26-강남구-06</v>
       </c>
       <c r="D27" t="str">
         <v>양호</v>
@@ -1896,30 +1896,30 @@
         <v>일반</v>
       </c>
       <c r="P27" t="str">
-        <v>-</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q27" t="str">
-        <v>역삼동826-21</v>
+        <v>역삼동831</v>
       </c>
       <c r="R27" t="str">
         <v/>
       </c>
       <c r="S27" t="str">
-        <v>미왕빌딩 앞 도로(강남대로364)</v>
+        <v>혜천빌딩 앞도로(강남대로354)</v>
       </c>
       <c r="T27" t="str">
-        <v/>
+        <v>22년 발생 첫조사'23년 아스콘 보수(패칭)'25년 아스콘 재보수(패칭)</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>26-06</v>
+        <v>26-07</v>
       </c>
       <c r="B28" t="str">
         <v>강남대로</v>
       </c>
       <c r="C28" t="str">
-        <v>26-강남구-06</v>
+        <v>26-강남구-07</v>
       </c>
       <c r="D28" t="str">
         <v>양호</v>
@@ -1958,16 +1958,16 @@
         <v>일반</v>
       </c>
       <c r="P28" t="str">
-        <v>5cm미만 침하</v>
+        <v>-</v>
       </c>
       <c r="Q28" t="str">
-        <v>역삼동831</v>
+        <v>역삼동831-7</v>
       </c>
       <c r="R28" t="str">
         <v/>
       </c>
       <c r="S28" t="str">
-        <v>혜천빌딩 앞도로(강남대로354)</v>
+        <v>현대자동차강남대로사옥 앞 도로(강남대로350)</v>
       </c>
       <c r="T28" t="str">
         <v/>
@@ -1975,13 +1975,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>26-07</v>
+        <v>26-08</v>
       </c>
       <c r="B29" t="str">
         <v>강남대로</v>
       </c>
       <c r="C29" t="str">
-        <v>26-강남구-07</v>
+        <v>26-강남구-08</v>
       </c>
       <c r="D29" t="str">
         <v>양호</v>
@@ -2023,13 +2023,13 @@
         <v>-</v>
       </c>
       <c r="Q29" t="str">
-        <v>역삼동831-7</v>
+        <v>우성아파트앞 사거리</v>
       </c>
       <c r="R29" t="str">
         <v/>
       </c>
       <c r="S29" t="str">
-        <v>현대자동차강남대로사옥 앞 도로(강남대로350)</v>
+        <v>교차로(강남대로346-2)</v>
       </c>
       <c r="T29" t="str">
         <v/>
@@ -2037,13 +2037,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>26-08</v>
+        <v>26-09</v>
       </c>
       <c r="B30" t="str">
         <v>강남대로</v>
       </c>
       <c r="C30" t="str">
-        <v>26-강남구-08</v>
+        <v>26-강남구-09</v>
       </c>
       <c r="D30" t="str">
         <v>양호</v>
@@ -2085,13 +2085,13 @@
         <v>-</v>
       </c>
       <c r="Q30" t="str">
-        <v>우성아파트앞 사거리</v>
+        <v>역삼동832-2</v>
       </c>
       <c r="R30" t="str">
         <v/>
       </c>
       <c r="S30" t="str">
-        <v>교차로(강남대로346-2)</v>
+        <v>더갤러리832 앞 도로(강남대로330)</v>
       </c>
       <c r="T30" t="str">
         <v/>
@@ -2099,13 +2099,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>26-09</v>
+        <v>26-10</v>
       </c>
       <c r="B31" t="str">
         <v>강남대로</v>
       </c>
       <c r="C31" t="str">
-        <v>26-강남구-09</v>
+        <v>26-강남구-10</v>
       </c>
       <c r="D31" t="str">
         <v>양호</v>
@@ -2147,13 +2147,13 @@
         <v>-</v>
       </c>
       <c r="Q31" t="str">
-        <v>역삼동832-2</v>
+        <v>역삼동837</v>
       </c>
       <c r="R31" t="str">
         <v/>
       </c>
       <c r="S31" t="str">
-        <v>더갤러리832 앞 도로(강남대로330)</v>
+        <v>타워837 앞 도로(강남대로318)</v>
       </c>
       <c r="T31" t="str">
         <v/>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>26-10</v>
+        <v>26-11</v>
       </c>
       <c r="B32" t="str">
         <v>강남대로</v>
       </c>
       <c r="C32" t="str">
-        <v>26-강남구-10</v>
+        <v>26-강남구-11</v>
       </c>
       <c r="D32" t="str">
         <v>양호</v>
@@ -2209,13 +2209,13 @@
         <v>-</v>
       </c>
       <c r="Q32" t="str">
-        <v>역삼동837</v>
+        <v>역삼동838</v>
       </c>
       <c r="R32" t="str">
         <v/>
       </c>
       <c r="S32" t="str">
-        <v>타워837 앞 도로(강남대로318)</v>
+        <v>KB라이프타워 앞 도로(강남대로298)</v>
       </c>
       <c r="T32" t="str">
         <v/>
@@ -2223,13 +2223,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>26-11</v>
+        <v>26-12</v>
       </c>
       <c r="B33" t="str">
         <v>강남대로</v>
       </c>
       <c r="C33" t="str">
-        <v>26-강남구-11</v>
+        <v>26-강남구-12</v>
       </c>
       <c r="D33" t="str">
         <v>양호</v>
@@ -2271,13 +2271,13 @@
         <v>-</v>
       </c>
       <c r="Q33" t="str">
-        <v>역삼동838</v>
+        <v>도곡동943</v>
       </c>
       <c r="R33" t="str">
         <v/>
       </c>
       <c r="S33" t="str">
-        <v>KB라이프타워 앞 도로(강남대로298)</v>
+        <v>뱅뱅빌딩 현대자동차 앞 도로(강남대로292)</v>
       </c>
       <c r="T33" t="str">
         <v/>
@@ -2285,13 +2285,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>26-12</v>
+        <v>26-13</v>
       </c>
       <c r="B34" t="str">
         <v>강남대로</v>
       </c>
       <c r="C34" t="str">
-        <v>26-강남구-12</v>
+        <v>26-강남구-13</v>
       </c>
       <c r="D34" t="str">
         <v>양호</v>
@@ -2333,13 +2333,13 @@
         <v>-</v>
       </c>
       <c r="Q34" t="str">
-        <v>도곡동943</v>
+        <v>도곡동949-1</v>
       </c>
       <c r="R34" t="str">
         <v/>
       </c>
       <c r="S34" t="str">
-        <v>뱅뱅빌딩 현대자동차 앞 도로(강남대로292)</v>
+        <v>도곡푸르지오아파트 앞 도로(강남대로54길6)</v>
       </c>
       <c r="T34" t="str">
         <v/>
@@ -2347,13 +2347,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>26-13</v>
+        <v>26-14</v>
       </c>
       <c r="B35" t="str">
         <v>강남대로</v>
       </c>
       <c r="C35" t="str">
-        <v>26-강남구-13</v>
+        <v>26-강남구-14</v>
       </c>
       <c r="D35" t="str">
         <v>양호</v>
@@ -2395,13 +2395,13 @@
         <v>-</v>
       </c>
       <c r="Q35" t="str">
-        <v>도곡동949-1</v>
+        <v>도곡동952</v>
       </c>
       <c r="R35" t="str">
         <v/>
       </c>
       <c r="S35" t="str">
-        <v>도곡푸르지오아파트 앞 도로(강남대로54길6)</v>
+        <v>대우양재디오빌 앞 도로(강남대로256)</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -2409,13 +2409,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>26-14</v>
+        <v>26-15</v>
       </c>
       <c r="B36" t="str">
         <v>강남대로</v>
       </c>
       <c r="C36" t="str">
-        <v>26-강남구-14</v>
+        <v>26-강남구-15</v>
       </c>
       <c r="D36" t="str">
         <v>양호</v>
@@ -2457,13 +2457,13 @@
         <v>-</v>
       </c>
       <c r="Q36" t="str">
-        <v>도곡동952</v>
+        <v>도곡동952-6</v>
       </c>
       <c r="R36" t="str">
         <v/>
       </c>
       <c r="S36" t="str">
-        <v>대우양재디오빌 앞 도로(강남대로256)</v>
+        <v>도루코사옥 앞 도로(강남대로254)</v>
       </c>
       <c r="T36" t="str">
         <v/>
@@ -2471,13 +2471,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>26-15</v>
+        <v>26-16</v>
       </c>
       <c r="B37" t="str">
         <v>강남대로</v>
       </c>
       <c r="C37" t="str">
-        <v>26-강남구-15</v>
+        <v>26-강남구-16</v>
       </c>
       <c r="D37" t="str">
         <v>양호</v>
@@ -2519,83 +2519,21 @@
         <v>-</v>
       </c>
       <c r="Q37" t="str">
-        <v>도곡동952-6</v>
+        <v>도곡동953</v>
       </c>
       <c r="R37" t="str">
         <v/>
       </c>
       <c r="S37" t="str">
-        <v>도루코사옥 앞 도로(강남대로254)</v>
+        <v>다림빌딩 앞 도로 (강남대로246)</v>
       </c>
       <c r="T37" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>26-16</v>
-      </c>
-      <c r="B38" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C38" t="str">
-        <v>26-강남구-16</v>
-      </c>
-      <c r="D38" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E38" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F38" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G38" t="str">
-        <v>14.5</v>
-      </c>
-      <c r="H38" t="str">
-        <v>-</v>
-      </c>
-      <c r="I38" t="str">
-        <v>0</v>
-      </c>
-      <c r="J38" t="str">
-        <v>3</v>
-      </c>
-      <c r="K38" t="str">
-        <v>0</v>
-      </c>
-      <c r="L38" t="str">
-        <v>1</v>
-      </c>
-      <c r="M38" t="str">
-        <v>0</v>
-      </c>
-      <c r="N38" t="str">
-        <v>4</v>
-      </c>
-      <c r="O38" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P38" t="str">
-        <v>-</v>
-      </c>
-      <c r="Q38" t="str">
-        <v>도곡동953</v>
-      </c>
-      <c r="R38" t="str">
-        <v/>
-      </c>
-      <c r="S38" t="str">
-        <v>다림빌딩 앞 도로 (강남대로246)</v>
-      </c>
-      <c r="T38" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T37"/>
   </ignoredErrors>
 </worksheet>
 </file>